--- a/src/test/output_test/Specific_Regions/Region_100_500_0/Files/1.xlsx
+++ b/src/test/output_test/Specific_Regions/Region_100_500_0/Files/1.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -393,7 +393,7 @@
         <v>101</v>
       </c>
       <c r="B2">
-        <v>393</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>102</v>
       </c>
       <c r="B3">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>103</v>
       </c>
       <c r="B4">
-        <v>373</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>104</v>
       </c>
       <c r="B5">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>105</v>
       </c>
       <c r="B6">
-        <v>290</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>106</v>
       </c>
       <c r="B7">
-        <v>302</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>107</v>
       </c>
       <c r="B8">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>108</v>
       </c>
       <c r="B9">
-        <v>292</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>109</v>
       </c>
       <c r="B10">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>110</v>
       </c>
       <c r="B11">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>111</v>
       </c>
       <c r="B12">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -481,7 +481,7 @@
         <v>112</v>
       </c>
       <c r="B13">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -489,7 +489,7 @@
         <v>113</v>
       </c>
       <c r="B14">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -497,7 +497,7 @@
         <v>114</v>
       </c>
       <c r="B15">
-        <v>225</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -505,7 +505,7 @@
         <v>115</v>
       </c>
       <c r="B16">
-        <v>202</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -513,7 +513,7 @@
         <v>116</v>
       </c>
       <c r="B17">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -521,7 +521,7 @@
         <v>117</v>
       </c>
       <c r="B18">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -529,7 +529,7 @@
         <v>118</v>
       </c>
       <c r="B19">
-        <v>184</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -537,7 +537,7 @@
         <v>119</v>
       </c>
       <c r="B20">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -545,7 +545,7 @@
         <v>120</v>
       </c>
       <c r="B21">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -553,7 +553,7 @@
         <v>121</v>
       </c>
       <c r="B22">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -561,7 +561,7 @@
         <v>122</v>
       </c>
       <c r="B23">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -569,7 +569,7 @@
         <v>123</v>
       </c>
       <c r="B24">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -577,7 +577,7 @@
         <v>124</v>
       </c>
       <c r="B25">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -585,7 +585,7 @@
         <v>125</v>
       </c>
       <c r="B26">
-        <v>118</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -593,7 +593,7 @@
         <v>126</v>
       </c>
       <c r="B27">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -601,7 +601,7 @@
         <v>127</v>
       </c>
       <c r="B28">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -609,7 +609,7 @@
         <v>128</v>
       </c>
       <c r="B29">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -617,7 +617,7 @@
         <v>129</v>
       </c>
       <c r="B30">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -625,7 +625,7 @@
         <v>130</v>
       </c>
       <c r="B31">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -633,7 +633,7 @@
         <v>131</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -641,7 +641,7 @@
         <v>132</v>
       </c>
       <c r="B33">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -649,7 +649,7 @@
         <v>133</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -657,7 +657,7 @@
         <v>134</v>
       </c>
       <c r="B35">
-        <v>105</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -665,7 +665,7 @@
         <v>135</v>
       </c>
       <c r="B36">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -673,7 +673,7 @@
         <v>136</v>
       </c>
       <c r="B37">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -681,7 +681,7 @@
         <v>137</v>
       </c>
       <c r="B38">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -689,7 +689,7 @@
         <v>138</v>
       </c>
       <c r="B39">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -697,7 +697,7 @@
         <v>139</v>
       </c>
       <c r="B40">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -705,7 +705,7 @@
         <v>140</v>
       </c>
       <c r="B41">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -713,7 +713,7 @@
         <v>141</v>
       </c>
       <c r="B42">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -721,7 +721,7 @@
         <v>142</v>
       </c>
       <c r="B43">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -729,7 +729,7 @@
         <v>143</v>
       </c>
       <c r="B44">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -737,7 +737,7 @@
         <v>144</v>
       </c>
       <c r="B45">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -745,7 +745,7 @@
         <v>145</v>
       </c>
       <c r="B46">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -753,7 +753,7 @@
         <v>146</v>
       </c>
       <c r="B47">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -761,7 +761,7 @@
         <v>147</v>
       </c>
       <c r="B48">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -769,7 +769,7 @@
         <v>148</v>
       </c>
       <c r="B49">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -777,7 +777,7 @@
         <v>149</v>
       </c>
       <c r="B50">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -793,7 +793,7 @@
         <v>151</v>
       </c>
       <c r="B52">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -801,7 +801,7 @@
         <v>152</v>
       </c>
       <c r="B53">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -809,7 +809,7 @@
         <v>153</v>
       </c>
       <c r="B54">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -825,7 +825,7 @@
         <v>155</v>
       </c>
       <c r="B56">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -833,7 +833,7 @@
         <v>156</v>
       </c>
       <c r="B57">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -841,7 +841,7 @@
         <v>157</v>
       </c>
       <c r="B58">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -849,7 +849,7 @@
         <v>158</v>
       </c>
       <c r="B59">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -857,7 +857,7 @@
         <v>159</v>
       </c>
       <c r="B60">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -865,7 +865,7 @@
         <v>160</v>
       </c>
       <c r="B61">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -873,7 +873,7 @@
         <v>161</v>
       </c>
       <c r="B62">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -881,7 +881,7 @@
         <v>162</v>
       </c>
       <c r="B63">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -897,7 +897,7 @@
         <v>164</v>
       </c>
       <c r="B65">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -905,7 +905,7 @@
         <v>165</v>
       </c>
       <c r="B66">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -913,7 +913,7 @@
         <v>166</v>
       </c>
       <c r="B67">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -921,7 +921,7 @@
         <v>167</v>
       </c>
       <c r="B68">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -929,7 +929,7 @@
         <v>168</v>
       </c>
       <c r="B69">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -937,7 +937,7 @@
         <v>169</v>
       </c>
       <c r="B70">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -945,7 +945,7 @@
         <v>170</v>
       </c>
       <c r="B71">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -953,7 +953,7 @@
         <v>171</v>
       </c>
       <c r="B72">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -961,7 +961,7 @@
         <v>172</v>
       </c>
       <c r="B73">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -969,7 +969,7 @@
         <v>173</v>
       </c>
       <c r="B74">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -977,7 +977,7 @@
         <v>174</v>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -985,7 +985,7 @@
         <v>175</v>
       </c>
       <c r="B76">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -993,7 +993,7 @@
         <v>176</v>
       </c>
       <c r="B77">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1001,7 +1001,7 @@
         <v>177</v>
       </c>
       <c r="B78">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1009,7 +1009,7 @@
         <v>178</v>
       </c>
       <c r="B79">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1017,7 +1017,7 @@
         <v>179</v>
       </c>
       <c r="B80">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1025,7 +1025,7 @@
         <v>180</v>
       </c>
       <c r="B81">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1033,7 +1033,7 @@
         <v>181</v>
       </c>
       <c r="B82">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1049,7 +1049,7 @@
         <v>183</v>
       </c>
       <c r="B84">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1057,7 +1057,7 @@
         <v>184</v>
       </c>
       <c r="B85">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1073,7 +1073,7 @@
         <v>186</v>
       </c>
       <c r="B87">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1081,7 +1081,7 @@
         <v>187</v>
       </c>
       <c r="B88">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>188</v>
       </c>
       <c r="B89">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1097,7 +1097,7 @@
         <v>189</v>
       </c>
       <c r="B90">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1105,7 +1105,7 @@
         <v>190</v>
       </c>
       <c r="B91">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1113,7 +1113,7 @@
         <v>191</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1121,7 +1121,7 @@
         <v>192</v>
       </c>
       <c r="B93">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1129,7 +1129,7 @@
         <v>193</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1137,7 +1137,7 @@
         <v>194</v>
       </c>
       <c r="B95">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1145,7 +1145,7 @@
         <v>195</v>
       </c>
       <c r="B96">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1153,7 +1153,7 @@
         <v>196</v>
       </c>
       <c r="B97">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1161,7 +1161,7 @@
         <v>197</v>
       </c>
       <c r="B98">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1169,7 +1169,7 @@
         <v>198</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1177,7 +1177,7 @@
         <v>199</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1185,7 +1185,7 @@
         <v>200</v>
       </c>
       <c r="B101">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1193,7 +1193,7 @@
         <v>201</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1201,7 +1201,7 @@
         <v>202</v>
       </c>
       <c r="B103">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1209,7 +1209,7 @@
         <v>203</v>
       </c>
       <c r="B104">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1217,7 +1217,7 @@
         <v>204</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1225,7 +1225,7 @@
         <v>205</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1233,7 +1233,7 @@
         <v>206</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1249,7 +1249,7 @@
         <v>208</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1265,7 +1265,7 @@
         <v>210</v>
       </c>
       <c r="B111">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1273,7 +1273,7 @@
         <v>211</v>
       </c>
       <c r="B112">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1289,7 +1289,7 @@
         <v>213</v>
       </c>
       <c r="B114">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1297,7 +1297,7 @@
         <v>214</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1305,7 +1305,7 @@
         <v>215</v>
       </c>
       <c r="B116">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1313,7 +1313,7 @@
         <v>216</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1345,7 +1345,7 @@
         <v>220</v>
       </c>
       <c r="B121">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1353,7 +1353,7 @@
         <v>221</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1361,7 +1361,7 @@
         <v>222</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1369,7 +1369,7 @@
         <v>223</v>
       </c>
       <c r="B124">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1385,7 +1385,7 @@
         <v>225</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1401,7 +1401,7 @@
         <v>227</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1417,7 +1417,7 @@
         <v>229</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1425,7 +1425,7 @@
         <v>230</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -1441,7 +1441,7 @@
         <v>232</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1449,7 +1449,7 @@
         <v>233</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>234</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1473,7 +1473,7 @@
         <v>236</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -1481,7 +1481,7 @@
         <v>237</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -1489,7 +1489,7 @@
         <v>238</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -1497,7 +1497,7 @@
         <v>239</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -1513,7 +1513,7 @@
         <v>241</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -1537,7 +1537,7 @@
         <v>244</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -1553,7 +1553,7 @@
         <v>246</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -1561,7 +1561,7 @@
         <v>247</v>
       </c>
       <c r="B148">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -1569,7 +1569,7 @@
         <v>248</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -1585,7 +1585,7 @@
         <v>250</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -1649,7 +1649,7 @@
         <v>258</v>
       </c>
       <c r="B159">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -1681,7 +1681,7 @@
         <v>262</v>
       </c>
       <c r="B163">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>268</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>275</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>280</v>
       </c>
       <c r="B181">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>281</v>
       </c>
       <c r="B182">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>298</v>
       </c>
       <c r="B199">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>306</v>
       </c>
       <c r="B207">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>307</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>308</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>312</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>314</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>337</v>
       </c>
       <c r="B238">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>343</v>
       </c>
       <c r="B244">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -2369,7 +2369,7 @@
         <v>348</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -2401,7 +2401,7 @@
         <v>352</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -2425,7 +2425,7 @@
         <v>355</v>
       </c>
       <c r="B256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -2569,7 +2569,7 @@
         <v>373</v>
       </c>
       <c r="B274">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -2577,7 +2577,7 @@
         <v>374</v>
       </c>
       <c r="B275">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -2601,7 +2601,7 @@
         <v>377</v>
       </c>
       <c r="B278">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -2657,7 +2657,7 @@
         <v>384</v>
       </c>
       <c r="B285">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -2761,7 +2761,7 @@
         <v>397</v>
       </c>
       <c r="B298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -2801,7 +2801,7 @@
         <v>402</v>
       </c>
       <c r="B303">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -2865,7 +2865,7 @@
         <v>410</v>
       </c>
       <c r="B311">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -2881,7 +2881,7 @@
         <v>412</v>
       </c>
       <c r="B313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -2961,7 +2961,7 @@
         <v>422</v>
       </c>
       <c r="B323">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -3041,7 +3041,7 @@
         <v>432</v>
       </c>
       <c r="B333">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -3049,7 +3049,7 @@
         <v>433</v>
       </c>
       <c r="B334">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -3321,6 +3321,214 @@
         <v>467</v>
       </c>
       <c r="B368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>468</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>469</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>470</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>471</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>472</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>473</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>474</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>475</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>476</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>477</v>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>478</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>479</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>480</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>481</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>482</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>483</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>484</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>485</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>486</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>487</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>488</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>489</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>490</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>491</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>492</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>493</v>
+      </c>
+      <c r="B394">
         <v>1</v>
       </c>
     </row>
